--- a/Pre-Week-3/homework1_exercise1A.xlsx
+++ b/Pre-Week-3/homework1_exercise1A.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\12406\Documents\DataAnalytics\Pre-Week-3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B1FF13A-3E80-4273-977F-AFD53C866450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7858221-2B95-47B8-84A3-73D60460F37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{58A641FA-BFDB-4A4C-A339-60E25DCCAEFF}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{58A641FA-BFDB-4A4C-A339-60E25DCCAEFF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -47,40 +47,40 @@
     <t>Average Rating</t>
   </si>
   <si>
-    <t>Introduction to Psychology</t>
+    <t>Introduction to Python</t>
   </si>
   <si>
-    <t>Digital Marketing 101</t>
+    <t>Data Analysis Basics</t>
   </si>
   <si>
-    <t>Data Science Bootcamp</t>
+    <t>Web Development 101</t>
   </si>
   <si>
-    <t>Basic Photography</t>
+    <t>Cybersecurity Fundamentals</t>
   </si>
   <si>
-    <t>Modern Web Development</t>
+    <t>Cloud Computing Intro</t>
   </si>
   <si>
-    <t>Creative Writing Workshop</t>
+    <t>Machine Learning Basics</t>
   </si>
   <si>
-    <t>Financial Literacy</t>
+    <t>SQL for Beginners</t>
   </si>
   <si>
-    <t>Advanced Java Programming</t>
+    <t>Excel for Data Analysis</t>
   </si>
   <si>
-    <t>Graphic Design Essentials</t>
+    <t>Java Programming</t>
   </si>
   <si>
-    <t>Public Speaking Mastery</t>
+    <t>Networking Essentials</t>
   </si>
   <si>
-    <t>Introduction to Sociology</t>
+    <t>AI Concepts</t>
   </si>
   <si>
-    <t>Machine Learning A-Z</t>
+    <t>Linux Administration</t>
   </si>
 </sst>
 </file>
@@ -112,7 +112,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -120,41 +120,55 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -165,6 +179,1156 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Enrollment</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Count</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:view3D>
+      <c:rotX val="15"/>
+      <c:rotY val="20"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="1"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:bar3DChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Enrollment Count</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>Introduction to Python</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Data Analysis Basics</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Web Development 101</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Cybersecurity Fundamentals</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Cloud Computing Intro</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Machine Learning Basics</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>SQL for Beginners</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Excel for Data Analysis</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Java Programming</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Networking Essentials</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>AI Concepts</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Linux Administration</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$B$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>220</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>260</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>310</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>170</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4C12-4754-BB3D-0DC699B6298E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Average Rating</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>Introduction to Python</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Data Analysis Basics</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Web Development 101</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Cybersecurity Fundamentals</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Cloud Computing Intro</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Machine Learning Basics</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>SQL for Beginners</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Excel for Data Analysis</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Java Programming</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Networking Essentials</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>AI Concepts</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Linux Administration</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$2:$C$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.5999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.4000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.8</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4C12-4754-BB3D-0DC699B6298E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:shape val="box"/>
+        <c:axId val="82913120"/>
+        <c:axId val="82913600"/>
+        <c:axId val="0"/>
+      </c:bar3DChart>
+      <c:catAx>
+        <c:axId val="82913120"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="82913600"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="82913600"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="82913120"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="286">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>99060</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>49530</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>403860</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56CD29A4-AC0B-B954-BC10-FCE74C67B5B8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5F8CAD0E-C0ED-494F-A971-1382C682237A}" name="Table3" displayName="Table3" ref="A1:C13" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+  <autoFilter ref="A1:C13" xr:uid="{5F8CAD0E-C0ED-494F-A971-1382C682237A}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{83671A01-EFA4-49B1-B210-A11E81CFBE78}" name="Course Name" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{6E9455FA-1FDE-4564-AD18-AD9965FD0300}" name="Enrollment Count" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{18888917-A769-4808-B793-D202C203B892}" name="Average Rating" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -484,161 +1648,162 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E3F607B-6CFB-47E3-906C-5DCFA6770198}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.109375" customWidth="1"/>
-    <col min="2" max="2" width="26.6640625" customWidth="1"/>
-    <col min="3" max="3" width="25.21875" customWidth="1"/>
+    <col min="1" max="1" width="24.21875" customWidth="1"/>
+    <col min="2" max="2" width="17.21875" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1">
-        <v>482</v>
-      </c>
-      <c r="C2" s="1">
+      <c r="B2" s="2">
+        <v>120</v>
+      </c>
+      <c r="C2" s="2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2">
+        <v>85</v>
+      </c>
+      <c r="C3" s="2">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2">
+        <v>200</v>
+      </c>
+      <c r="C4" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2">
+        <v>150</v>
+      </c>
+      <c r="C5" s="2">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2">
+        <v>300</v>
+      </c>
+      <c r="C6" s="2">
         <v>4.7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+    <row r="7" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2">
+        <v>220</v>
+      </c>
+      <c r="C7" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="2">
+        <v>95</v>
+      </c>
+      <c r="C8" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2">
+        <v>180</v>
+      </c>
+      <c r="C9" s="2">
         <v>4</v>
       </c>
-      <c r="B3" s="1">
-        <v>315</v>
-      </c>
-      <c r="C3" s="1">
+    </row>
+    <row r="10" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2">
+        <v>260</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="2">
+        <v>140</v>
+      </c>
+      <c r="C11" s="2">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="2">
+        <v>310</v>
+      </c>
+      <c r="C12" s="2">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="2">
+        <v>170</v>
+      </c>
+      <c r="C13" s="2">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="1">
-        <v>495</v>
-      </c>
-      <c r="C4" s="1">
-        <v>4.9000000000000004</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1">
-        <v>120</v>
-      </c>
-      <c r="C5" s="1">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="1">
-        <v>340</v>
-      </c>
-      <c r="C6" s="1">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="1">
-        <v>85</v>
-      </c>
-      <c r="C7" s="1">
-        <v>4.0999999999999996</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="1">
-        <v>210</v>
-      </c>
-      <c r="C8" s="1">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="1">
-        <v>158</v>
-      </c>
-      <c r="C9" s="1">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="1">
-        <v>275</v>
-      </c>
-      <c r="C10" s="1">
-        <v>4.5999999999999996</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="1">
-        <v>62</v>
-      </c>
-      <c r="C11" s="1">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="1">
-        <v>390</v>
-      </c>
-      <c r="C12" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="1">
-        <v>412</v>
-      </c>
-      <c r="C13" s="1">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>